--- a/Data/Building/TeaRoom.Curtain001.xlsx
+++ b/Data/Building/TeaRoom.Curtain001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H264"/>
+  <dimension ref="A1:I296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709252643</v>
+        <v>1711844303</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -505,6 +510,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,7 +529,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709256785</v>
+        <v>1711844478</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -541,6 +547,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -559,7 +566,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709260286</v>
+        <v>1711845555</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -577,6 +584,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -595,7 +603,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709262696</v>
+        <v>1711853166</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -613,6 +621,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -631,7 +640,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709262711</v>
+        <v>1711853211</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -649,6 +658,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -667,7 +677,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709265909</v>
+        <v>1711854315</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -685,6 +695,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -703,7 +714,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709265915</v>
+        <v>1711859786</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -721,6 +732,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -739,7 +751,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709269232</v>
+        <v>1711860718</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -757,6 +769,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -775,7 +788,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709269270</v>
+        <v>1711860729</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -793,6 +806,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -811,7 +825,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709247489</v>
+        <v>1711868438</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -829,6 +843,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -847,7 +862,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709251420</v>
+        <v>1711868452</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -865,6 +880,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -883,7 +899,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709252737</v>
+        <v>1711926636</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -901,6 +917,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -919,7 +936,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709252747</v>
+        <v>1711928833</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -937,6 +954,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -955,7 +973,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709253320</v>
+        <v>1711930932</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -973,6 +991,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -991,7 +1010,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709253348</v>
+        <v>1711931867</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1009,6 +1028,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1027,7 +1047,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709254807</v>
+        <v>1711932115</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1045,6 +1065,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1063,7 +1084,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709254822</v>
+        <v>1711932337</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1081,6 +1102,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1099,7 +1121,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709260110</v>
+        <v>1711936356</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1117,6 +1139,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1135,7 +1158,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709263415</v>
+        <v>1711936364</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1153,6 +1176,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1171,7 +1195,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709267055</v>
+        <v>1711937291</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1189,6 +1213,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1207,7 +1232,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709332085</v>
+        <v>1711937312</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1225,6 +1250,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1243,7 +1269,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709334375</v>
+        <v>1711941580</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1261,6 +1287,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1279,7 +1306,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709335348</v>
+        <v>1711941587</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1297,6 +1324,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1315,7 +1343,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709339092</v>
+        <v>1711945734</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1333,6 +1361,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1351,7 +1380,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709339108</v>
+        <v>1711948704</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1369,6 +1398,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1387,7 +1417,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709345771</v>
+        <v>1712016946</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1405,6 +1435,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1423,7 +1454,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709345783</v>
+        <v>1712016961</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1441,6 +1472,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1459,7 +1491,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709348450</v>
+        <v>1712019029</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1477,6 +1509,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1495,7 +1528,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709348861</v>
+        <v>1712019039</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1513,6 +1546,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1531,7 +1565,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709351241</v>
+        <v>1712019795</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1549,6 +1583,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1567,7 +1602,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709351262</v>
+        <v>1712019871</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1585,6 +1620,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1603,7 +1639,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709354254</v>
+        <v>1712021013</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1621,6 +1657,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1639,7 +1676,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709354267</v>
+        <v>1712021021</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1657,6 +1694,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1675,7 +1713,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709354634</v>
+        <v>1712024038</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1693,6 +1731,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1711,7 +1750,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709356125</v>
+        <v>1712024042</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1729,6 +1768,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1747,7 +1787,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709426128</v>
+        <v>1712025022</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1765,6 +1805,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1783,7 +1824,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709426148</v>
+        <v>1712025036</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1801,6 +1842,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1819,7 +1861,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709426713</v>
+        <v>1712028920</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1837,6 +1879,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1855,7 +1898,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709426844</v>
+        <v>1712028937</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1873,6 +1916,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1891,7 +1935,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709429787</v>
+        <v>1712030833</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1909,6 +1953,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1927,7 +1972,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709432707</v>
+        <v>1712031531</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1945,6 +1990,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1963,7 +2009,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709445995</v>
+        <v>1712098358</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1981,6 +2027,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1999,7 +2046,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709446003</v>
+        <v>1712098372</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2017,6 +2064,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2035,7 +2083,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709512660</v>
+        <v>1712105963</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2053,6 +2101,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2071,7 +2120,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709512681</v>
+        <v>1712106001</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2089,6 +2138,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2107,7 +2157,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709513266</v>
+        <v>1712107128</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2125,6 +2175,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2143,7 +2194,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709513285</v>
+        <v>1712108055</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2161,6 +2212,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2179,7 +2231,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709515882</v>
+        <v>1712110273</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2197,6 +2249,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2215,7 +2268,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709515893</v>
+        <v>1712110281</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2233,6 +2286,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2251,7 +2305,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709523425</v>
+        <v>1712112253</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2269,6 +2323,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2287,7 +2346,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709524889</v>
+        <v>1712112910</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2305,6 +2364,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2323,7 +2383,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709524957</v>
+        <v>1712124005</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2341,6 +2401,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2359,7 +2420,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1709524965</v>
+        <v>1712124019</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2377,6 +2438,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2395,7 +2457,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1709525715</v>
+        <v>1712182039</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2413,6 +2475,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2431,7 +2494,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1709530224</v>
+        <v>1712182043</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2449,6 +2512,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2467,7 +2531,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1709592314</v>
+        <v>1712182554</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2485,6 +2549,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2503,7 +2572,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1709592341</v>
+        <v>1712182571</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2521,6 +2590,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2539,7 +2609,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1709598517</v>
+        <v>1712187000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2557,6 +2627,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2575,7 +2650,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1709598537</v>
+        <v>1712189422</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2593,6 +2668,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2611,7 +2687,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1709599963</v>
+        <v>1712198680</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2629,6 +2705,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2647,7 +2724,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1709599984</v>
+        <v>1712198704</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2665,6 +2742,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2683,7 +2761,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1709601173</v>
+        <v>1712199576</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2701,6 +2779,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2719,7 +2798,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1709601207</v>
+        <v>1712199586</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2737,6 +2816,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2755,7 +2835,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1709602319</v>
+        <v>1712275114</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2773,6 +2853,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2791,7 +2872,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1709602338</v>
+        <v>1712275122</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2809,6 +2890,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2827,7 +2909,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1709608812</v>
+        <v>1712276427</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2845,6 +2927,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2863,7 +2946,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1709608881</v>
+        <v>1712276693</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2881,6 +2964,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2899,7 +2983,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1709609357</v>
+        <v>1712277130</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2917,6 +3001,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2935,7 +3020,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1709609362</v>
+        <v>1712277145</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2953,6 +3038,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2971,7 +3057,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1709609417</v>
+        <v>1712281751</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2989,6 +3075,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3007,7 +3094,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1709609431</v>
+        <v>1712282335</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3025,6 +3112,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3043,7 +3131,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1709613470</v>
+        <v>1712290745</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3061,6 +3149,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3079,7 +3168,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1709613686</v>
+        <v>1712290757</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3097,6 +3186,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3115,7 +3205,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1709615775</v>
+        <v>1712369916</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3133,6 +3223,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3151,7 +3242,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1709615781</v>
+        <v>1712369929</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3169,6 +3260,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3187,7 +3279,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1709686455</v>
+        <v>1712454397</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3205,6 +3297,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3223,7 +3316,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1709689725</v>
+        <v>1712454409</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3241,6 +3334,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3259,7 +3353,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1709692131</v>
+        <v>1712454462</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3277,6 +3371,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3295,7 +3390,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1709692142</v>
+        <v>1712454473</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3313,6 +3408,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3331,7 +3427,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1709773710</v>
+        <v>1712459895</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3349,6 +3445,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3367,7 +3464,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1709773724</v>
+        <v>1712462899</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3385,6 +3482,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3403,7 +3501,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1709775724</v>
+        <v>1712530190</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3421,6 +3519,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3439,7 +3538,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1709779014</v>
+        <v>1712530200</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3457,6 +3556,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3475,7 +3575,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1709849374</v>
+        <v>1712535541</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3493,6 +3593,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3511,7 +3612,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1709849592</v>
+        <v>1712535866</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3529,6 +3630,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3547,7 +3649,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1709849829</v>
+        <v>1712536673</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3565,6 +3667,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3583,7 +3686,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1709849840</v>
+        <v>1712536691</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3601,6 +3704,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3619,7 +3723,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1709852195</v>
+        <v>1712538873</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3637,6 +3741,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3655,7 +3764,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1709852205</v>
+        <v>1712538891</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3673,6 +3782,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3691,7 +3801,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1709857070</v>
+        <v>1712539055</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3709,6 +3819,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3727,7 +3838,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1709857086</v>
+        <v>1712539067</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3745,6 +3856,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3763,7 +3875,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1709861317</v>
+        <v>1712546689</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3781,6 +3893,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3799,7 +3912,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1709861325</v>
+        <v>1712546698</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3817,6 +3930,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3835,7 +3949,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1709865851</v>
+        <v>1712548895</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3853,6 +3967,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3871,7 +3986,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1709865915</v>
+        <v>1712548903</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3889,6 +4004,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3907,7 +4023,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1709867447</v>
+        <v>1712549849</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3925,6 +4041,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3943,7 +4060,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1709867462</v>
+        <v>1712549867</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3961,6 +4078,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3979,7 +4097,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1709943690</v>
+        <v>1712550084</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3997,6 +4115,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4015,7 +4134,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1709943709</v>
+        <v>1712550553</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -4033,6 +4152,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4051,7 +4171,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1709948418</v>
+        <v>1712553451</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -4069,6 +4189,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4087,7 +4208,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1709948435</v>
+        <v>1712553458</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -4105,6 +4226,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4123,7 +4245,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1709948517</v>
+        <v>1712624831</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -4141,6 +4263,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4159,7 +4282,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1709948527</v>
+        <v>1712624876</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -4177,6 +4300,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4195,7 +4319,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1709954043</v>
+        <v>1712629726</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4213,6 +4337,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4231,7 +4356,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1709955459</v>
+        <v>1712630369</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -4249,6 +4374,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4267,7 +4393,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1709957665</v>
+        <v>1712630486</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -4285,6 +4411,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4303,7 +4430,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1709957685</v>
+        <v>1712630511</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -4321,6 +4448,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4339,7 +4467,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1710033816</v>
+        <v>1712633905</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -4357,6 +4485,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4375,7 +4504,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1710033828</v>
+        <v>1712633926</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -4393,6 +4522,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4411,7 +4541,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1710034296</v>
+        <v>1712712180</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -4429,6 +4559,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4447,7 +4578,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1710034311</v>
+        <v>1712712196</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4465,6 +4596,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4483,7 +4615,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1710051444</v>
+        <v>1712712362</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4501,6 +4633,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4519,7 +4652,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1710051455</v>
+        <v>1712712391</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4537,6 +4670,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4555,7 +4689,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1710110981</v>
+        <v>1712719795</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4573,6 +4707,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4591,7 +4726,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1710111001</v>
+        <v>1712719817</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4609,6 +4744,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4627,7 +4763,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1710120137</v>
+        <v>1712720894</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4645,6 +4781,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4663,7 +4800,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1710120162</v>
+        <v>1712720911</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4681,6 +4818,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4699,7 +4837,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1710120433</v>
+        <v>1712723481</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4717,6 +4855,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4735,7 +4874,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1710120451</v>
+        <v>1712723503</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4753,6 +4892,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4771,7 +4911,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1710124556</v>
+        <v>1712728504</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4789,6 +4929,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4807,7 +4948,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1710124577</v>
+        <v>1712730407</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4825,6 +4966,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4843,7 +4985,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1710127373</v>
+        <v>1712790825</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4861,6 +5003,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4879,7 +5022,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1710127387</v>
+        <v>1712790872</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4897,6 +5040,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4915,7 +5059,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1710128313</v>
+        <v>1712798929</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4933,6 +5077,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4951,7 +5096,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1710128323</v>
+        <v>1712799045</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4969,6 +5114,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4987,7 +5133,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1710134465</v>
+        <v>1712799621</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -5005,6 +5151,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5023,7 +5170,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1710134476</v>
+        <v>1712799630</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -5041,6 +5188,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5059,7 +5207,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1710196186</v>
+        <v>1712799854</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -5077,6 +5225,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5095,7 +5244,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1710197179</v>
+        <v>1712799862</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -5113,6 +5262,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5131,7 +5281,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1710204430</v>
+        <v>1712800736</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -5149,6 +5299,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5167,7 +5318,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1710204468</v>
+        <v>1712803893</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -5185,6 +5336,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5203,7 +5355,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1710204493</v>
+        <v>1712806521</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -5221,6 +5373,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5239,7 +5392,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1710204575</v>
+        <v>1712806551</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -5257,6 +5410,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5275,7 +5429,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1710204609</v>
+        <v>1712807130</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -5293,6 +5447,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5311,7 +5466,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1710204622</v>
+        <v>1712809407</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -5329,6 +5484,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5347,7 +5503,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1710214519</v>
+        <v>1712811150</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -5365,6 +5521,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5383,7 +5540,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1710214525</v>
+        <v>1712811169</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -5401,6 +5558,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5419,7 +5577,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1710217346</v>
+        <v>1712875773</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -5437,6 +5595,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5455,7 +5614,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1710225074</v>
+        <v>1712875796</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -5473,6 +5632,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5491,7 +5651,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1710301204</v>
+        <v>1712880051</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -5509,6 +5669,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5527,7 +5688,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1710301216</v>
+        <v>1712880060</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -5545,6 +5706,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5563,7 +5725,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1710378257</v>
+        <v>1712881905</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5581,6 +5743,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5599,7 +5762,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1710383228</v>
+        <v>1712883565</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5617,6 +5780,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5635,7 +5799,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1710385203</v>
+        <v>1712883762</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5653,6 +5817,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5671,7 +5836,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1710385211</v>
+        <v>1712883768</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5689,6 +5854,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5707,7 +5873,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1710456368</v>
+        <v>1712889704</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5725,6 +5891,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5743,7 +5910,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1710456382</v>
+        <v>1712889713</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5761,6 +5928,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5779,7 +5947,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1710462684</v>
+        <v>1712890092</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5797,6 +5965,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5815,7 +5984,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1710463322</v>
+        <v>1712890104</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5833,6 +6002,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5851,7 +6021,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1710463328</v>
+        <v>1712890579</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5869,6 +6039,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5887,7 +6062,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1710463546</v>
+        <v>1712891821</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5905,6 +6080,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5923,7 +6099,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1710468268</v>
+        <v>1712894597</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5941,6 +6117,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5959,7 +6140,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1710468284</v>
+        <v>1712896191</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5977,6 +6158,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5995,7 +6177,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1710468814</v>
+        <v>1712974630</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -6013,6 +6195,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6031,7 +6214,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1710468840</v>
+        <v>1712974645</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -6049,6 +6232,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6067,7 +6251,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1710468844</v>
+        <v>1713055553</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -6085,6 +6269,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6103,7 +6288,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1710468870</v>
+        <v>1713058853</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -6121,6 +6306,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6139,7 +6325,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1710469826</v>
+        <v>1713061416</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -6157,6 +6343,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6175,7 +6362,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1710469834</v>
+        <v>1713061428</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -6193,6 +6380,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6211,7 +6399,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1710474282</v>
+        <v>1713136192</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -6229,6 +6417,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6247,7 +6440,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1710474288</v>
+        <v>1713138578</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -6265,6 +6458,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6283,7 +6477,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1710475027</v>
+        <v>1713141315</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -6301,6 +6495,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6319,7 +6514,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1710475060</v>
+        <v>1713141328</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -6337,6 +6532,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6355,7 +6551,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1710475451</v>
+        <v>1713145680</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -6373,6 +6569,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6391,7 +6588,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1710475464</v>
+        <v>1713145709</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -6409,6 +6606,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6427,7 +6625,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1710541859</v>
+        <v>1713145834</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -6445,6 +6643,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6463,7 +6662,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1710541870</v>
+        <v>1713145850</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -6481,6 +6680,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6499,7 +6699,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1710548712</v>
+        <v>1713148480</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -6517,6 +6717,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6535,7 +6736,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1710548988</v>
+        <v>1713148485</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -6553,6 +6754,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6571,7 +6773,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1710549906</v>
+        <v>1713149097</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -6589,6 +6791,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6607,7 +6810,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1710549919</v>
+        <v>1713149103</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -6625,6 +6828,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6643,7 +6847,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1710557241</v>
+        <v>1713149174</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -6661,6 +6865,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6679,7 +6884,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1710557266</v>
+        <v>1713149187</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6697,6 +6902,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6715,7 +6921,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1710569389</v>
+        <v>1713149555</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6733,6 +6939,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6751,7 +6958,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1710569397</v>
+        <v>1713150276</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -6769,6 +6976,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6787,7 +6995,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1710630533</v>
+        <v>1713154699</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -6805,6 +7013,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6823,7 +7032,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1710630551</v>
+        <v>1713154702</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -6841,6 +7050,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6859,7 +7069,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1710637222</v>
+        <v>1713227859</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6877,6 +7087,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6895,7 +7106,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1710637230</v>
+        <v>1713227870</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6913,6 +7124,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6931,7 +7143,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1710639019</v>
+        <v>1713228060</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6949,6 +7161,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6967,7 +7180,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1710639034</v>
+        <v>1713228121</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -6985,6 +7198,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7003,7 +7217,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1710649762</v>
+        <v>1713236369</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -7021,6 +7235,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7039,7 +7258,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1710649776</v>
+        <v>1713236446</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -7057,6 +7276,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7075,7 +7295,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1710650870</v>
+        <v>1713238299</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -7093,6 +7313,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -7111,7 +7332,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1710650898</v>
+        <v>1713238784</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -7129,6 +7350,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -7147,7 +7369,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1710717427</v>
+        <v>1713307220</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -7165,6 +7387,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -7183,7 +7406,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1710717434</v>
+        <v>1713307232</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -7201,6 +7424,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -7219,7 +7443,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1710719959</v>
+        <v>1713312346</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -7237,6 +7461,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -7255,7 +7480,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1710719985</v>
+        <v>1713312356</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -7273,6 +7498,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -7291,7 +7517,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1710723294</v>
+        <v>1713314000</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -7309,6 +7535,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -7327,7 +7558,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1710723597</v>
+        <v>1713314045</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -7345,6 +7576,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -7363,7 +7595,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>1710723709</v>
+        <v>1713314055</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -7381,6 +7613,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7399,7 +7632,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1710724079</v>
+        <v>1713314156</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -7417,6 +7650,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -7435,7 +7669,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1710733242</v>
+        <v>1713314287</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -7453,6 +7687,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -7471,7 +7706,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1710737394</v>
+        <v>1713314321</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -7489,6 +7724,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -7507,7 +7743,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1710738448</v>
+        <v>1713315816</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -7525,6 +7761,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -7543,7 +7780,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1710738462</v>
+        <v>1713318202</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -7561,6 +7798,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -7579,7 +7817,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1710812029</v>
+        <v>1713322396</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -7597,6 +7835,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7615,7 +7854,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1710814078</v>
+        <v>1713322412</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -7633,6 +7872,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -7651,7 +7891,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1710817125</v>
+        <v>1713325748</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -7669,6 +7909,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -7687,7 +7928,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1710817132</v>
+        <v>1713325764</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -7705,6 +7946,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7723,7 +7965,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1710817945</v>
+        <v>1713331495</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -7741,6 +7983,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7759,7 +8002,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1710817959</v>
+        <v>1713391863</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -7777,6 +8020,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7795,7 +8039,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1710822667</v>
+        <v>1713397800</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -7813,6 +8057,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7831,7 +8080,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>1710822676</v>
+        <v>1713399169</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -7849,6 +8098,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7867,7 +8117,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1710898674</v>
+        <v>1713402170</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -7885,6 +8135,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7903,7 +8154,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>1710898684</v>
+        <v>1713402178</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -7921,6 +8172,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7939,7 +8191,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1710989422</v>
+        <v>1713402234</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -7957,6 +8209,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7975,7 +8228,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1710989561</v>
+        <v>1713403347</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -7993,6 +8246,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -8011,7 +8265,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1710991438</v>
+        <v>1713403680</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -8029,6 +8283,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -8047,7 +8302,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1710991463</v>
+        <v>1713403723</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -8065,6 +8320,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -8083,7 +8339,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1710991618</v>
+        <v>1713403761</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -8101,6 +8357,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -8119,7 +8376,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1710991627</v>
+        <v>1713403772</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -8137,6 +8394,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -8155,7 +8413,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>1710993110</v>
+        <v>1713406475</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -8173,6 +8431,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -8191,7 +8450,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>1710993127</v>
+        <v>1713406482</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -8209,6 +8468,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -8227,7 +8487,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1710995332</v>
+        <v>1713406840</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -8245,6 +8505,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -8263,7 +8524,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>1710995342</v>
+        <v>1713406848</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -8281,6 +8542,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -8299,7 +8561,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>1711059761</v>
+        <v>1713487484</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -8317,6 +8579,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -8335,7 +8598,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1711059820</v>
+        <v>1713487495</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -8353,6 +8616,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -8371,7 +8635,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1711067580</v>
+        <v>1713492421</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -8389,6 +8653,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -8407,7 +8672,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>1711067595</v>
+        <v>1713493461</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -8425,6 +8690,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -8443,7 +8709,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1711069584</v>
+        <v>1713499480</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -8461,6 +8727,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8479,7 +8746,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>1711069597</v>
+        <v>1713499486</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -8497,6 +8764,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -8515,7 +8783,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>1711074327</v>
+        <v>1713501206</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -8533,6 +8801,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -8551,7 +8820,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1711074347</v>
+        <v>1713501222</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -8569,6 +8838,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -8587,7 +8857,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>1711078982</v>
+        <v>1713574402</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -8605,6 +8875,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -8623,7 +8894,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>1711078989</v>
+        <v>1713574412</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -8641,6 +8912,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -8659,7 +8931,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>1711079689</v>
+        <v>1713576421</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -8677,6 +8949,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -8695,7 +8968,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>1711079711</v>
+        <v>1713576431</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -8713,6 +8986,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -8731,7 +9005,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>1711087696</v>
+        <v>1713664385</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -8749,6 +9023,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -8767,7 +9042,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>1711146342</v>
+        <v>1713664409</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -8785,6 +9060,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -8803,7 +9079,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>1711146597</v>
+        <v>1713669924</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -8821,6 +9097,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -8839,7 +9116,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>1711146619</v>
+        <v>1713669937</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -8857,6 +9134,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -8875,7 +9153,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>1711148978</v>
+        <v>1713738805</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -8893,6 +9171,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -8911,7 +9190,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>1711149093</v>
+        <v>1713738822</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -8929,6 +9208,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8947,7 +9227,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>1711172140</v>
+        <v>1713752964</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -8965,6 +9245,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8983,7 +9264,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>1711234470</v>
+        <v>1713752976</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -9001,6 +9282,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -9019,7 +9301,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>1711239941</v>
+        <v>1713754083</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -9037,6 +9319,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -9055,7 +9338,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>1711239957</v>
+        <v>1713754406</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -9073,6 +9356,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -9091,7 +9375,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>1711248300</v>
+        <v>1713824355</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -9109,6 +9393,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -9127,7 +9412,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>1711249740</v>
+        <v>1713824362</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -9145,6 +9430,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -9163,7 +9449,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>1711254667</v>
+        <v>1713831562</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -9181,6 +9467,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -9199,7 +9490,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>1711256120</v>
+        <v>1713832742</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -9217,6 +9508,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -9235,7 +9527,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>1711319581</v>
+        <v>1713833297</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -9253,6 +9545,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -9271,7 +9564,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>1711319594</v>
+        <v>1713834092</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -9289,6 +9582,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -9307,7 +9601,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>1711327774</v>
+        <v>1713836169</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -9325,6 +9619,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -9343,7 +9638,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>1711327792</v>
+        <v>1713836185</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -9361,6 +9656,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -9379,7 +9675,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>1711333881</v>
+        <v>1713843774</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -9397,6 +9693,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -9415,7 +9712,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>1711333896</v>
+        <v>1713843794</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -9433,6 +9730,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -9451,7 +9749,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>1711340995</v>
+        <v>1713844046</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -9469,6 +9767,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -9487,7 +9786,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>1711341011</v>
+        <v>1713844058</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -9505,6 +9804,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -9523,7 +9823,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>1711409956</v>
+        <v>1713846061</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -9541,6 +9841,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -9559,7 +9860,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>1711409961</v>
+        <v>1713846074</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -9577,6 +9878,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -9595,7 +9897,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>1711423315</v>
+        <v>1713917522</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -9613,6 +9915,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -9631,7 +9934,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>1711423332</v>
+        <v>1713917528</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -9649,6 +9952,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -9667,7 +9971,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>1711427407</v>
+        <v>1713918609</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -9685,6 +9989,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -9703,7 +10008,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>1711427474</v>
+        <v>1713918616</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -9721,6 +10026,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -9739,7 +10045,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>1711428530</v>
+        <v>1713920514</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -9757,6 +10063,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -9775,7 +10082,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>1711428550</v>
+        <v>1713920537</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -9793,6 +10100,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -9811,7 +10119,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>1711592620</v>
+        <v>1713924721</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -9829,6 +10137,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -9847,7 +10156,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>1711593222</v>
+        <v>1713924729</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -9865,6 +10174,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -9883,7 +10193,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>1711602438</v>
+        <v>1713926491</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -9901,6 +10211,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -9919,7 +10230,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>1711602455</v>
+        <v>1713926502</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -9937,6 +10248,1191 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>1713932895</v>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: open</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>1713937163</v>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: close</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>1713998939</v>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: open</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>1713998967</v>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: close</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>1713999079</v>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: open</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>1713999086</v>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: close</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D271" t="n">
+        <v>1714002340</v>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: open</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D272" t="n">
+        <v>1714002356</v>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: close</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>1714002844</v>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: open</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>1714002869</v>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: close</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>1714010694</v>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: open</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D276" t="n">
+        <v>1714010713</v>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: close</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D277" t="n">
+        <v>1714010988</v>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: open</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D278" t="n">
+        <v>1714011190</v>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: close</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D279" t="n">
+        <v>1714083919</v>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: open</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D280" t="n">
+        <v>1714084963</v>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: close</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D281" t="n">
+        <v>1714090806</v>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: open</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D282" t="n">
+        <v>1714090814</v>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: close</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D283" t="n">
+        <v>1714094134</v>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: open</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D284" t="n">
+        <v>1714094146</v>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: close</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D285" t="n">
+        <v>1714097735</v>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr"/>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: open</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D286" t="n">
+        <v>1714097765</v>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: close</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D287" t="n">
+        <v>1714104588</v>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: open</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D288" t="n">
+        <v>1714104605</v>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr"/>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: close</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D289" t="n">
+        <v>1714106760</v>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: open</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D290" t="n">
+        <v>1714106767</v>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: close</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D291" t="n">
+        <v>1714179480</v>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr"/>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: open</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D292" t="n">
+        <v>1714179494</v>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: close</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D293" t="n">
+        <v>1714179983</v>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr"/>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: open</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D294" t="n">
+        <v>1714179994</v>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr"/>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: close</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D295" t="n">
+        <v>1714270942</v>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr"/>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: open</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Curtain_Operation</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>TeaRoom</t>
+        </is>
+      </c>
+      <c r="D296" t="n">
+        <v>1714271131</v>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>TeaRoom.Curtain001.state: close</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
